--- a/data/trans_dic/IP25A_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Provincia-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 24,12</t>
+          <t>10,47; 26,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 24,26</t>
+          <t>8,23; 22,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 20,86</t>
+          <t>10,91; 21,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 28,74</t>
+          <t>13,22; 27,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,04; 26,74</t>
+          <t>15,65; 30,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 25,45</t>
+          <t>16,0; 25,85</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 14,74</t>
+          <t>2,12; 11,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,93</t>
+          <t>3,74; 15,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,84</t>
+          <t>3,79; 10,8</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 23,44</t>
+          <t>8,67; 29,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 30,85</t>
+          <t>7,93; 24,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 23,84</t>
+          <t>10,36; 23,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>5,2; 26,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 23,87</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 14,56</t>
+          <t>3,29; 14,95</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,43; 31,31</t>
+          <t>8,5; 24,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 23,65</t>
+          <t>12,99; 32,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,96; 23,8</t>
+          <t>12,8; 24,42</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,1; 30,86</t>
+          <t>12,96; 24,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,95; 23,85</t>
+          <t>16,53; 29,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,28; 24,67</t>
+          <t>15,66; 24,75</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,93</t>
+          <t>2,88; 9,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,26</t>
+          <t>0,66; 5,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,54</t>
+          <t>2,36; 6,47</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,42</t>
+          <t>11,64; 16,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,52; 16,22</t>
+          <t>11,52; 16,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,79</t>
+          <t>12,11; 15,52</t>
         </is>
       </c>
     </row>
@@ -1029,18 +1029,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>19096</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5419; 17675</t>
+          <t>6718; 17007</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8127; 19253</t>
+          <t>4646; 12493</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15962; 31838</t>
+          <t>13164; 26452</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>23081</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>44959</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11199; 36115</t>
+          <t>15313; 31669</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16635; 34114</t>
+          <t>15549; 30151</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32049; 64446</t>
+          <t>34429; 55613</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>7671</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2099; 8443</t>
+          <t>1258; 6906</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1352; 8016</t>
+          <t>2081; 8760</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4204; 13494</t>
+          <t>4357; 12423</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>22405</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5300; 15447</t>
+          <t>6124; 21168</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7019; 23653</t>
+          <t>5305; 16310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15815; 33990</t>
+          <t>14256; 32261</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5221</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2855</t>
+          <t>2059; 10609</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1865; 9720</t>
+          <t>0; 2524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2356; 10955</t>
+          <t>2472; 11243</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17132</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5737; 14457</t>
+          <t>4159; 11759</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4305; 13287</t>
+          <t>5945; 15051</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12237; 24358</t>
+          <t>12125; 23132</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>25347</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26564</t>
+          <t>26076</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>51423</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19387; 37155</t>
+          <t>18173; 34846</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18477; 36879</t>
+          <t>19573; 35402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42025; 67853</t>
+          <t>40505; 64014</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>12038</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>798; 7763</t>
+          <t>4585; 14678</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4497; 14487</t>
+          <t>925; 8300</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7203; 18806</t>
+          <t>7044; 19337</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>89730</t>
+          <t>96010</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>72364; 107420</t>
+          <t>81248; 112983</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>87401; 123075</t>
+          <t>71183; 99093</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>171524; 223073</t>
+          <t>159367; 204211</t>
         </is>
       </c>
     </row>
